--- a/questionnaire_templates/029_photo_limit_efficiency_quiz--questionnaire_templates.xlsx
+++ b/questionnaire_templates/029_photo_limit_efficiency_quiz--questionnaire_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -872,8 +872,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="33" customWidth="1" min="2" max="2"/>
-    <col width="33" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -935,12 +935,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'option':_'very_high'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'option': 'Very High'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -952,12 +952,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'option':_'high'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'option': 'High'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -969,12 +969,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'option':_'medium'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'option': 'Medium'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -986,12 +986,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'option':_'low'}</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'option': 'Low'}</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'option':_'very_low'}</t>
+          <t>option_5</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'option': 'Very Low'}</t>
+          <t>Option 5</t>
         </is>
       </c>
     </row>
@@ -1020,12 +1020,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'option':_'art'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'option': 'Art'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1037,12 +1037,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'option':_'biology'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'option': 'Biology'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1054,12 +1054,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'option':_'business'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'option': 'Business'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'option':_'engineering'}</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'option': 'Engineering'}</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -1088,12 +1088,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'option':_'history'}</t>
+          <t>option_5</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'option': 'History'}</t>
+          <t>Option 5</t>
         </is>
       </c>
     </row>
@@ -1105,12 +1105,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'option':_'math'}</t>
+          <t>option_6</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'option': 'Math'}</t>
+          <t>Option 6</t>
         </is>
       </c>
     </row>
@@ -1122,12 +1122,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'option':_'music'}</t>
+          <t>option_7</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'option': 'Music'}</t>
+          <t>Option 7</t>
         </is>
       </c>
     </row>
@@ -1139,12 +1139,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'option':_'physical_sciences'}</t>
+          <t>option_8</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'option': 'Physical Sciences'}</t>
+          <t>Option 8</t>
         </is>
       </c>
     </row>
@@ -1156,12 +1156,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'option':_'technology'}</t>
+          <t>option_9</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'option': 'Technology'}</t>
+          <t>Option 9</t>
         </is>
       </c>
     </row>
@@ -1173,12 +1173,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'option':_'10_gb'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'option': '10 GB'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1190,12 +1190,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'option':_'100_gb'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'option': '100 GB'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1207,12 +1207,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'option':_'1_tb'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'option': '1 TB'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1224,12 +1224,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'option':_'10_tb'}</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'option': '10 TB'}</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -1241,12 +1241,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'option':_'other'}</t>
+          <t>option_5</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'option': 'Other'}</t>
+          <t>Option 5</t>
         </is>
       </c>
     </row>
@@ -1258,12 +1258,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'option':_'100_kb'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'option': '100 KB'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1275,12 +1275,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'option':_'1000_kb'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'option': '1000 KB'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1292,12 +1292,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'option':_'1000_mb'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'option': '1000 MB'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1309,12 +1309,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'option':_'1000_mb'}</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'option': '1000 MB'}</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -1326,12 +1326,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'option':_'other'}</t>
+          <t>option_5</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'option': 'Other'}</t>
+          <t>Option 5</t>
         </is>
       </c>
     </row>
@@ -1343,12 +1343,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'option':_'$0-$10'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'option': '$0-$10'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1360,12 +1360,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'option':_'$10-$50'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'option': '$10-$50'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1377,12 +1377,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'option':_'$50-$100'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'option': '$50-$100'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1394,12 +1394,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'option':_'$100-$500'}</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'option': '$100-$500'}</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -1411,12 +1411,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'option':_'$500_or_more'}</t>
+          <t>option_5</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'option': '$500 or more'}</t>
+          <t>Option 5</t>
         </is>
       </c>
     </row>
@@ -1428,12 +1428,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'option':_'$0'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'option': '$0'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1445,12 +1445,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'option':_'$1-$10'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'option': '$1-$10'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1462,12 +1462,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'option':_'$10-$50'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'option': '$10-$50'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1479,12 +1479,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'option':_'$50-$100'}</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'option': '$50-$100'}</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -1496,12 +1496,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'option':_'$100_or_more'}</t>
+          <t>option_5</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'option': '$100 or more'}</t>
+          <t>Option 5</t>
         </is>
       </c>
     </row>
@@ -1513,12 +1513,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'option':_'very_high'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'option': 'Very High'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1530,12 +1530,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'option':_'high'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'option': 'High'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1547,12 +1547,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'option':_'medium'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'option': 'Medium'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1564,12 +1564,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{'option':_'low'}</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{'option': 'Low'}</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>{'option':_'very_low'}</t>
+          <t>option_5</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{'option': 'Very Low'}</t>
+          <t>Option 5</t>
         </is>
       </c>
     </row>
@@ -1598,12 +1598,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>{'option':_'very_high'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{'option': 'Very High'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1615,12 +1615,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>{'option':_'high'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>{'option': 'High'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1632,12 +1632,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>{'option':_'medium'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>{'option': 'Medium'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1649,12 +1649,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>{'option':_'low'}</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>{'option': 'Low'}</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -1666,12 +1666,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>{'option':_'very_low'}</t>
+          <t>option_5</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>{'option': 'Very Low'}</t>
+          <t>Option 5</t>
         </is>
       </c>
     </row>
